--- a/.cursor/scratch/tax_turbo_parts/827 Grove CapEx.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/827 Grove CapEx.xlsx
@@ -588,7 +588,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Prime HD / Lowe’s / IKEA — Grove 1/3 (user split 2026-09-18)</t>
+          <t>Prime HD / Lowe’s / IKEA — 827 N Grove the house 1/3 (NOT Grove Collaborative supplies)</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>CPA: this 1/3 is pre-close hardware/furniture (close 2025-12-18). Do NOT fold into locked TY2025 CapEx $53,660 (the 2025-12-19 contractor payments) until you say so. May be additional 827 basis / CapEx / personal — FLAG.</t>
+          <t>CPA: this 1/3 is pre-close hardware/furniture for 827 N Grove the house (close 2025-12-18). This is NOT Grove Collaborative. Do NOT fold into locked TY2025 CapEx $53,660 (the 2025-12-19 contractor payments) until you say so. May be additional 827 basis / CapEx / personal — FLAG.</t>
         </is>
       </c>
     </row>
